--- a/samples/ss_paiton123_ingest.xlsx
+++ b/samples/ss_paiton123_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -844,19 +824,16 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>1 IBT x 500 MVA (unit 2); beban &gt;90%</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -872,7 +849,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -901,35 +877,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>bus A1/B1 - A2/B2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -958,23 +925,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>60/20/60 MVA</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -990,7 +950,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1019,23 +978,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>20/20/60 MVA</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1051,7 +1003,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1080,23 +1031,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>30/60/30 MVA + 25 MVAR + SVC (+50/-25 MVAR)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1112,7 +1056,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1141,23 +1084,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>60/60/60 MVA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1173,7 +1109,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1202,23 +1137,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>4x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1234,7 +1162,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1263,35 +1190,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>60 MVA + 2x25 MVAR</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1320,23 +1238,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1352,7 +1263,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1381,23 +1291,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>3x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1413,7 +1316,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1442,35 +1344,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1499,35 +1392,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>25 MVA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1556,35 +1440,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>1x30 MW</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1613,17 +1488,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>ujung Kabel Laut SKLT Jawa-Bali</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1649,7 +1518,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1756,7 +1624,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Paiton - Gending</t>
@@ -1777,7 +1644,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1791,8 +1657,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1809,13 +1673,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Paiton - Kraksaan</t>
@@ -1836,7 +1698,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1850,8 +1711,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1868,7 +1727,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1899,7 +1757,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1913,8 +1770,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1931,7 +1786,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1962,7 +1816,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -1976,8 +1829,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1994,7 +1845,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2025,7 +1875,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2039,8 +1888,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2057,7 +1904,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2088,7 +1934,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -2102,8 +1947,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2120,7 +1963,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2151,7 +1993,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -2165,8 +2006,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2183,13 +2022,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Jember - Puger</t>
@@ -2210,7 +2047,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2224,8 +2060,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2242,13 +2076,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Jember - Tanggul</t>
@@ -2269,7 +2101,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2283,8 +2114,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2301,7 +2130,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2332,7 +2160,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2346,8 +2173,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2364,13 +2189,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Bondowoso - Jember</t>
@@ -2391,7 +2214,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2405,8 +2227,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2423,13 +2243,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Outlet PLTP Ijen - Genteng</t>
@@ -2450,7 +2268,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -2464,8 +2281,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2482,7 +2297,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2513,7 +2327,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>4</v>
       </c>
@@ -2527,8 +2340,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -2545,7 +2356,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2624,12 +2434,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT 2 Paiton dengan total target sebesar 178MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton -Bali. 3. Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
+          <t>1. Sudah terpasang OLS IBT 2 Paiton dengan total target sebesar 178 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton - Bali. 3. Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Penambahan IBT-4 di GITET Paiton. (hasil dari action Tracker dipilih IBT -4 Paiton Untuk Solusi Shorterm) (Berdasarkan RUPTL 2025 - 2034, COD Base Tahun 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo,COD Tahun 2026. 6. Pembangunan PLTS 150 kV dengan total 50 MW di Paiton (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menegah : 7. Pembangunan PLTS 150 kV dengan Total 50 MW di Watudodol (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029). 8. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). Usulan / Solusi 9. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 10.Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 11.Pembangunan PLTP Iyang Argopurodan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL). 12.Pembangunan PLTS Jawa Timur di Probolinggo (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
+          <t>Jangka Pendek: 1. Penambahan IBT-4 di GITET Paiton. (hasil dari action Tracker dipilih IBT - 4 Paiton Untuk Solusi Shorterm) (Berdasarkan RUPTL 2025 - 2034, COD Base Tahun 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. 6. Pembangunan PLTS 150 kV dengan total 50 MW di Paiton (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menegah : 7. Pembangunan PLTS 150 kV dengan Total 50 MW di Watudodol (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029). 8. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). Usulan / Solusi 9. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 10. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). Jangka Panjang : 11. Pembangunan PLTP Iyang Argopurodan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL). 12. Pembangunan PLTS Jawa Timur di Probolinggo (Berdasarkan RUPTL 2025 - 2034, COD diluar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2459,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] IBT-1,3 500/150 kV Paitonsudahberbeban diatas 80% sehingga sudah tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] IBT-1,3 500/150 kV Paiton sudah berbeban diatas 80% sehingga sudah tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2659,12 +2469,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT 1,3Paiton dengan total target sebesar 775 MW (berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton -Bali. 3. Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
+          <t>1. Sudah terpasang OLS IBT 1,3 Paiton dengan total target sebesar 775 MW (berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton - Bali. 3. Dioperasikan Pararel 3 IBT di GI Paiton 1 Busbar, Per 10 Februari 2025</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 2. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo,COD Tahun 2026. 4. Pembangunan PLTS 150 kV dengan total 50 MW di Paiton (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah: 5. Pembangunan PLTS 150 kV dengan Total 50 MW di Usulan / Solusi Watudodol (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029). 6. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). 7. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 8. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 2. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. 4. Pembangunan PLTS 150 kV dengan total 50 MW di Paiton (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah : 5. Pembangunan PLTS 150 kV dengan Total 50 MW di Usulan / Solusi Watudodol (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029). 6. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). 7. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 8. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2494,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] PembebananSUTT 150 kV Paiton- Situbondo1&amp;2 &gt;90% sehingga tidak memenuhikriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Paiton- Situbondo1&amp;2 &gt;90% sehingga tidak memenuhi kriteriaN-1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2694,12 +2504,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS di SUTT 150 kV Paiton-Situbondo dengan total target sebesar775 MW(berdasarkan Deklasarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme(ADS) Paiton -Bali. 3. Saat ada pekerjaan pemeliharaan, pengaturan transfer ke Bali dibatasi &lt;50 MW. 4. Pembatasan transfer ke Bali normal 270 MW</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Paiton-Situbondo dengan total target sebesar 775 MW (berdasarkan Deklasarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Scheme (ADS) Paiton - Bali. 3. Saat ada pekerjaan pemeliharaan, pengaturan transfer ke Bali dibatasi &lt;50 MW. 4. Pembatasan transfer ke Bali normal 270 MW</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rekonduktoring SUTT 150 kV Paiton-Situbondo (Berdasarkan RUPTL 2025 - 2034, COD Base Tahun 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo,COD Tahun 2026. Jangka Menengah: 5. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). Usulan / Solusi 6. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 7. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1. Rekonduktoring SUTT 150 kV Paiton-Situbondo (Berdasarkan RUPTL 2025 - 2034, COD Base Tahun 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. Jangka Menengah : 5. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). Usulan / Solusi 6. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 7. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2529,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Situbondo- Bondowoso 1&amp;2 &gt;60% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Situbondo- Bondowoso 1&amp;2 &gt;60% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. TerjadiOverloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
+          <t>1. Terjadi Overloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2734,7 +2544,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 2. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Dilakukan rekonfigurasi Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo,COD Tahun 2026. Jangka Menengah: 4. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030)</t>
+          <t>Jangka Pendek : 1. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 2. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Dilakukan rekonfigurasi Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. Jangka Menengah : 4. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030)</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2564,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] PembebananSUTT 150 kV Situbondo- Banyuwangi 1&amp;2 &gt;65% sehingga tidak memenuhikriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Situbondo- Banyuwangi 1&amp;2 &gt;65% sehingga tidak memenuhi kriteriaN-1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. TerjadiOverloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
+          <t>1. Terjadi Overloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT 150 kV Situbondo- Banyuwangi dengan total target sebesar 496 MW(berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Mitigasi Scheme (ADS) Paiton -Bali. 3. Pekerjaan dilakukan saat beban rendah. 4. Sudah terpasangN-2 SUTT 150 kV Situbondo- Banyuwangi untuk membuat island Subsistem Bali</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Situbondo- Banyuwangi dengan total target sebesar 496 MW (berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang Adaptive Defense Mitigasi Scheme (ADS) Paiton - Bali. 3. Pekerjaan dilakukan saat beban rendah. 4. Sudah terpasang N-2 SUTT 150 kV Situbondo- Banyuwangi untuk membuat island Subsistem Bali</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 2. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - Usulan / Solusi 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo,COD Tahun 2026. Jangka Menengah: 4. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). 5. Pembangunan PLTB 150 kV dengan total 80MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 6. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 2. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - Usulan / Solusi 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. Jangka Menengah : 4. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). 5. Pembangunan PLTB 150 kV dengan total 80MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 6. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -2789,22 +2599,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Lumajang-Tanggul 1&amp;2 &gt;60% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Lumajang-Tanggul 1&amp;2 &gt;60% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. TerjadiOverloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
+          <t>1. Terjadi Overloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT 150 kV Lumajang-Tanggul dengan total target sebesar358 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Lumajang-Tanggul dengan total target sebesar 358 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Rekonduktoring SUTT 150 kV Lumajang- Tanggul-Jember. (Berdasarkan RUPTL 2025 - 2034, COD Base Tahun 2026. 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Usulan / Solusi Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. Jangka Menengah: 5. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). 6. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 7. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1. Percepatan Rekonduktoring SUTT 150 kV Lumajang- Tanggul-Jember. (Berdasarkan RUPTL 2025 - 2034, COD Base Tahun 2026. 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Dilakukan rekonfigurasi Subsistem setelah GITET Watudodol beroperasi dimana konfigurasi IBT 1,2 Usulan / Solusi Paiton memasok melalui jalur SUTT Paiton-Kraksaan dan IBT 3 Paiton akan looping jauh dengan IBT 1,2 GITET Watudodol untuk memasok melalui SUTT Paiton- Situbondo, COD Tahun 2026. Jangka Menengah : 5. Pembangunan proyek Jawa Bali Connection (JBC) dan GITET Antosari. (Berdasarkan RUPTL 2025 - 2034 COD di 2030). 6. Pembangunan PLTB 150 kV dengan total 80 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 7. Pembangunan PLTB 150 kV dengan total 100 MW di Banyuwangi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2634,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan tidak seimbang karena konfigurasi single phi pada SUTT 150 kV Jember-Genteng dan Genteng-Banyuwangi dan pembebanan sudah mencapai &gt;60% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan tidak seimbang karena konfigurasi single phi pada SUTT 150 kV Jember-Genteng dan Genteng-Banyuwangi dan pembebanan sudah mencapai &gt;60% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. TerjadiOverloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
+          <t>1. Terjadi Overloadjika terjadi trip pada salah satu ruas penghantar tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2839,7 +2649,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Normalisasi konfigurasi Double Phi menjadi SUTT 150 kV Banyuwangi-Genteng dan SUTT 150 kV Genteng- Jember. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 2. Rekonduktoring SUTT 150 kV Banyuwangi-Genteng- Jember menjadi 2cct, HTLSC 1600 A per sirkit, setelah GITET Watudodol beroperasi di Tahun 2025 karena akan menjadi outlet dari IBT tersebut. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek: 1. Normalisasi konfigurasi Double Phi menjadi SUTT 150 kV Banyuwangi-Genteng dan SUTT 150 kV Genteng- Jember. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 2. Rekonduktoring SUTT 150 kV Banyuwangi-Genteng- Jember menjadi 2cct, HTLSC 1600 A per sirkit, setelah GITET Watudodol beroperasi di Tahun 2025 karena akan menjadi outlet dari IBT tersebut. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
